--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2ace04cb63d84493"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1cd2eb73052541e8"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Re238fbb986444411"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rf3fda4347aa04217"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1cd2eb73052541e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R52ec9d95dd694d4f"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rf3fda4347aa04217"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Reb7c83cd5a2d4a12"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R52ec9d95dd694d4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7cd36df6319f4f11"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Reb7c83cd5a2d4a12"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R338cabedb7ad4c16"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7cd36df6319f4f11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R838c89957435426b"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R338cabedb7ad4c16"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rb9fde7fbd2c443e5"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R838c89957435426b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra5914b569d78432c"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rb9fde7fbd2c443e5"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R0637cc70bede4508"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra5914b569d78432c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2652975497294821"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R0637cc70bede4508"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R31fc488d79f34c45"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2652975497294821"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf266a2b54b3d4a23"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R31fc488d79f34c45"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R00c10d9651b24a8d"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf266a2b54b3d4a23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbfc91f89914f46e3"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R00c10d9651b24a8d"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rdaf272b7d90a4ce3"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbfc91f89914f46e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2e4b7905a5204d2a"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rdaf272b7d90a4ce3"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Re0a7327866a5437e"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2e4b7905a5204d2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R76046fecbf7344ca"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Re0a7327866a5437e"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R8ca0530b973c4146"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R76046fecbf7344ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc971b492af484b03"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R8ca0530b973c4146"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R0a695458d1ac4854"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc971b492af484b03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R18c4e5360ee6454e"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R0a695458d1ac4854"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R474907d3b5b24951"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R18c4e5360ee6454e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra82bcd9d4e3646e6"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R474907d3b5b24951"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R87a1d14099404325"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra82bcd9d4e3646e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0087b7acf516483f"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R87a1d14099404325"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rd2730eedfc6149d1"/>
   </x:pivotCaches>
 </x:workbook>
 </file>
